--- a/output/虐待防止委員会_研修実施報告書_R8.8.20.xlsx
+++ b/output/虐待防止委員会_研修実施報告書_R8.8.20.xlsx
@@ -510,7 +510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:D14"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -519,6 +519,7 @@
     <col width="45" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -533,6 +534,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="24" customHeight="1">
       <c r="B5" s="3" t="inlineStr">
         <is>
@@ -606,7 +608,7 @@
       <c r="C10" s="5" t="inlineStr">
         <is>
           <t>委員長：生田友哉
-委員：WIN YADANAR AUNG、吉田俊輔、吉田麻美</t>
+委員：WIN YADANAR AUNG、吉田駿成、吉田麻美</t>
         </is>
       </c>
       <c r="D10" s="7" t="n"/>

--- a/output/虐待防止委員会_研修実施報告書_R8.8.20.xlsx
+++ b/output/虐待防止委員会_研修実施報告書_R8.8.20.xlsx
@@ -510,7 +510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="B2:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -519,7 +519,6 @@
     <col width="45" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -534,7 +533,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="24" customHeight="1">
       <c r="B5" s="3" t="inlineStr">
         <is>

--- a/output/虐待防止委員会_研修実施報告書_R8.8.20.xlsx
+++ b/output/虐待防止委員会_研修実施報告書_R8.8.20.xlsx
@@ -508,7 +508,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B2:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
@@ -679,6 +679,8 @@
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="B2:D2"/>
   </mergeCells>
+  <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>